--- a/structural_model/examples/MLK/model_geometry.xlsx
+++ b/structural_model/examples/MLK/model_geometry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel.MIGUEL-DESK\Documents\GitHub\RC_Column_Model\structural_model\examples\MLK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18598CE5-0855-4677-95FB-D5488A96BFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D87C02B-F5D6-4BFE-BB64-2FE6D311F5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16965" yWindow="1515" windowWidth="18780" windowHeight="13470" activeTab="1" xr2:uid="{BF1D43A3-CD0A-4BDB-BB7F-2C5FE7E3DE72}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25890" windowHeight="15555" activeTab="1" xr2:uid="{BF1D43A3-CD0A-4BDB-BB7F-2C5FE7E3DE72}"/>
   </bookViews>
   <sheets>
     <sheet name="modelInfo" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="693">
   <si>
     <t>pier</t>
   </si>
@@ -2114,6 +2114,12 @@
   </si>
   <si>
     <t>10001</t>
+  </si>
+  <si>
+    <t>p01</t>
+  </si>
+  <si>
+    <t>p02</t>
   </si>
 </sst>
 </file>
@@ -3401,6 +3407,2255 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>nodeInfo!$B$2:$B$328</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="327"/>
+                <c:pt idx="0">
+                  <c:v>14982.044900000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14304.67</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13867.809499999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13397.9809</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12914.040800000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12418.366599999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11743.536</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11293.729799999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10848.534600000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10416.2606</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9995.6399000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9419.8268000000007</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9093.6429000000007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8786.5195999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8511.3863999999994</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8257.7464999999993</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7929.6471000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7743.9377000000004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7582.5762999999997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7440.7723999999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7355.3967000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7229.7803000000004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7173.7794999999996</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7140.9323000000004</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7112.1720999999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7077.9198999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7075.7464</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7074.2871999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7073.3473999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7072.2825999999995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7071.4062999999996</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7070.4488000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7069.3675000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7068.1661999999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7067.5573999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7067.1833999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7067.1095999999998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7067.6234999999997</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7068.2584999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7069.0995000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7070.1307999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7072.2025000000003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7073.634</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>7075.1619000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7076.7437</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7079.4229999999998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7081.5583999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7083.5851000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7085.4818999999998</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7087.4763000000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7088.4461000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7089.0217000000002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7089.0969999999998</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7088.5864000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7086.5002000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7084.3401999999996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7082.1512000000002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7080.6212999999998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7080.3845000000001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7083.8936000000003</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7097.3450999999995</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>7106.7071999999998</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7136.8689000000004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>14982.044900000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>14982.044900000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>14304.67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>13867.809499999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>13397.9809</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>12914.040800000001</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>12418.366599999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>11743.536</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>11293.729799999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>10848.534600000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>10416.2606</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>9995.6399000000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9419.8268000000007</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>9093.6429000000007</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>8786.5195999999996</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>8511.3863999999994</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>8257.7464999999993</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>7929.6471000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>7743.9377000000004</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>7582.5762999999997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7440.7723999999998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>7355.3967000000002</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7229.7803000000004</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>7173.7794999999996</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>7140.9323000000004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>7112.1720999999998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>7077.9198999999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>7075.7464</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>7074.2871999999998</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>7073.3473999999997</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>7072.2825999999995</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>7071.4062999999996</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>7070.4488000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>7069.3675000000003</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>7068.1661999999997</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>7067.5573999999997</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>7067.1833999999999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>7067.1095999999998</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>7067.6234999999997</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>7068.2584999999999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>7069.0995000000003</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>7070.1307999999999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>7072.2025000000003</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>7073.634</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>7075.1619000000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>7076.7437</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>7079.4229999999998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>7081.5583999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>7083.5851000000002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>7085.4818999999998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>7087.4763000000003</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7088.4461000000001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>7089.0217000000002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>7089.0969999999998</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>7088.5864000000001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7086.5002000000004</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>7084.3401999999996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>7082.1512000000002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>7080.6212999999998</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>7080.3845000000001</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>7083.8936000000003</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>7097.3450999999995</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7106.7071999999998</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7136.8689000000004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7136.8689000000004</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>14982.044900000001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>14304.67</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>13867.809499999999</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>13397.9809</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>12914.040800000001</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>12418.366599999999</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>11743.536</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>11293.729799999999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>10848.534600000001</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>10416.2606</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>9995.6399000000001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>9419.8268000000007</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>9093.6429000000007</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>8786.5195999999996</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>8511.3863999999994</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>8257.7464999999993</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>7929.6471000000001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>7743.9377000000004</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>7582.5762999999997</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>7440.7723999999998</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>7355.3967000000002</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>7229.7803000000004</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>7173.7794999999996</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>7140.9323000000004</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>7112.1720999999998</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>7077.9198999999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>7075.7464</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>7074.2871999999998</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>7073.3473999999997</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>7072.2825999999995</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>7071.4062999999996</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>7070.4488000000001</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>7069.3675000000003</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>7068.1661999999997</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>7067.5573999999997</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>7067.1833999999999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>7067.1095999999998</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>7067.6234999999997</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>7068.2584999999999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>7069.0995000000003</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>7070.1307999999999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>7072.2025000000003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>7073.634</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>7075.1619000000001</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>7076.7437</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>7079.4229999999998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>7081.5583999999999</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>7083.5851000000002</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>7085.4818999999998</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>7087.4763000000003</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>7088.4461000000001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>7089.0217000000002</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>7089.0969999999998</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>7088.5864000000001</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>7086.5002000000004</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>7084.3401999999996</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>7082.1512000000002</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>7080.6212999999998</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>7080.3845000000001</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>7083.8936000000003</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>7089.1617999999999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>7097.3450999999995</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>7106.7071999999998</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>7136.8689000000004</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>14892.727888458328</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>14217.204303193686</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>13781.410888656334</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>13312.315034555531</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>12832.192359687766</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>12337.848238792065</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>11662.230282149038</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>11211.001462401293</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>10763.942185023712</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>10329.436694098702</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>9906.0954978364643</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>9327.5392878853618</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>9000.4505660967625</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>8685.4477778645905</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>8417.3130294572238</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>8163.3845763031668</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>7835.3561248640808</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>7649.9302510971584</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>7488.7840978825752</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>7347.636205925487</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>7263.2401229494526</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>7139.3219140417468</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>7084.4877870660785</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>7052.886029055574</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>7025.2851520457689</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>7003.2921561159956</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>6993.3800678626949</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>6991.7224750018195</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>6990.2872306364543</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>6989.3474257579546</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>6988.2826404699008</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>6987.4063485364231</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>6986.4488488730094</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>6985.3675382295769</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>6984.1662217468311</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>6983.5574081406021</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>6983.1834003193644</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>6983.1096059699621</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>6983.6235256314867</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>6984.2585455945518</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>6985.0995677733699</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>6986.1308974203594</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>6988.202624779602</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>6989.6341413368673</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>6991.1620533543119</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>6992.7438608572693</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>6995.4231583604742</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>6997.5585459143895</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>6999.5852252446784</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>7001.48198992999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>7003.4763478508876</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>7004.4461165435514</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>7005.0217002863119</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>7005.0970133219644</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>7004.5864973148273</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>7002.5004386938963</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>7000.3404397470949</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>6998.1513181457585</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>6996.6213029160672</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>6996.3847733860348</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>6999.9192564179057</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>7004.8898692879229</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>7012.5129145507044</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>7022.7239119028072</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>7052.9063813592038</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>15071.361911541673</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>14392.135696806314</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>13954.208111343665</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>13483.64676544447</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>12995.889240312235</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>12498.884961207934</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>11824.841717850963</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>11376.458137598705</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>10933.12701497629</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>10503.084505901297</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>10085.184302163536</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>9512.1143121146397</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>9186.835233903239</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>8887.5914221354087</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>8605.459770542775</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>8352.1084236968309</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>8023.9380751359195</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>7837.9451489028424</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>7676.3685021174242</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>7533.9085940745126</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>7447.5532770505479</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>7320.2386859582539</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>7263.0712129339208</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>7228.9785709444268</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>7199.0590479542307</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>7175.0314438840041</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>7162.4597321373049</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>7159.7703249981805</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>7158.2871693635452</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>7157.3473742420447</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>7156.2825595300983</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>7155.4062514635762</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>7154.4487511269908</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>7153.3674617704237</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>7152.1661782531683</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>7151.5573918593973</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>7151.1833996806354</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>7151.1095940300374</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>7151.6234743685127</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>7152.258454405448</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>7153.0994322266306</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>7154.1307025796405</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>7156.2023752203986</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>7157.6338586631327</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>7159.1617466456883</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>7160.7435391427307</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>7163.4228416395254</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>7165.5582540856103</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>7167.584974755322</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>7169.4818100700095</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>7171.476252149113</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>7172.4460834564488</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>7173.0216997136886</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>7173.0969866780351</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>7172.586302685173</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>7170.4999613061045</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>7168.3399602529043</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>7166.151081854242</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>7164.6212970839324</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>7164.3842266139654</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>7167.867943582095</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>7173.4337307120768</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>7182.1772854492947</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>7190.6904880971924</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>7220.831418640797</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>nodeInfo!$C$2:$C$328</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="327"/>
+                <c:pt idx="0">
+                  <c:v>2332.9126999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4154.5767999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5164.9093999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6174.7349000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7168.0447000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8162.5126</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9518.3803000000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10440.243200000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11371.7016</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12298.7942</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13238.549800000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14640.3976</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15514.191800000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>16390.671300000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17281.751899999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18179.9833</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19510.650000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>20422.172299999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21332.774300000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22382.569200000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>23160.0831</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>24528.586500000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>25421.793099999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26315.517400000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27207.753700000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28097.487099999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>29615.037899999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30705.7196</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>31797.8269</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>32898.2019</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>34257.8825</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>35150.5942</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36041.289900000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>37043.678500000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>38302.8249</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>39148.885000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>39998.393900000003</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>40844.719599999997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>42207.787400000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>43020.639199999998</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>43827.8073</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>44639.664900000003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>45999.938499999997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46830.446300000003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>47663.3433</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>48491.147499999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>49860.215499999998</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>50959.929799999998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>52047.267599999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>53145.681600000004</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>54508.645299999996</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>55417.222099999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>56334.352299999999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>57246.363100000002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>58152.974699999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>59523.511500000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>60429.571199999998</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>61345.7765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>62257.951500000003</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>63156.636599999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>64532.043400000002</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>65370.7952</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>66203.498900000006</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>66893.224900000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>68405.054000000004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2332.9126999999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2332.9126999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4154.5767999999998</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5164.9093999999996</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6174.7349000000004</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7168.0447000000004</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>8162.5126</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9518.3803000000007</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>10440.243200000001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>11371.7016</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>12298.7942</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>13238.549800000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>14640.3976</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>15514.191800000001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>16390.671300000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>17281.751899999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>18179.9833</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>19510.650000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20422.172299999998</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>21332.774300000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>22382.569200000002</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>23160.0831</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>24528.586500000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>25421.793099999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>26315.517400000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>27207.753700000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>28097.487099999998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>29615.037899999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>30705.7196</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>31797.8269</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>32898.2019</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>34257.8825</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>35150.5942</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>36041.289900000003</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>37043.678500000002</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>38302.8249</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>39148.885000000002</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>39998.393900000003</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>40844.719599999997</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>42207.787400000001</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>43020.639199999998</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>43827.8073</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>44639.664900000003</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>45999.938499999997</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46830.446300000003</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>47663.3433</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>48491.147499999999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>49860.215499999998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>50959.929799999998</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>52047.267599999999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>53145.681600000004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>54508.645299999996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>55417.222099999999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>56334.352299999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>57246.363100000002</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>58152.974699999999</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>59523.511500000001</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>60429.571199999998</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>61345.7765</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>62257.951500000003</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>63156.636599999998</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>64532.043400000002</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>65370.7952</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>66203.498900000006</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>66893.224900000001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>68405.054000000004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>68405.054000000004</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2332.9126999999999</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4154.5767999999998</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5164.9093999999996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>6174.7349000000004</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>7168.0447000000004</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>8162.5126</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>9518.3803000000007</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>10440.243200000001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>11371.7016</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>12298.7942</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>13238.549800000001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>14640.3976</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15514.191800000001</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>16390.671300000002</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>17281.751899999999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>18179.9833</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>19510.650000000001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>20422.172299999998</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>21332.774300000001</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>22382.569200000002</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>23160.0831</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>24528.586500000001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>25421.793099999999</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>26315.517400000001</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>27207.753700000001</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>28097.487099999998</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>29615.037899999999</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>30705.7196</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>31797.8269</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>32898.2019</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>34257.8825</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>35150.5942</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>36041.289900000003</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>37043.678500000002</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>38302.8249</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>39148.885000000002</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>39998.393900000003</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>40844.719599999997</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>42207.787400000001</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>43020.639199999998</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>43827.8073</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>44639.664900000003</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>45999.938499999997</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>46830.446300000003</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>47663.3433</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>48491.147499999999</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>49860.215499999998</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>50959.929799999998</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>52047.267599999999</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>53145.681600000004</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>54508.645299999996</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>55417.222099999999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>56334.352299999999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>57246.363100000002</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>58152.974699999999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>59523.511500000001</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>60429.571199999998</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>61345.7765</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>62257.951500000003</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>63156.636599999998</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>64532.043400000002</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>65370.7952</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>66203.498900000006</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>66893.224900000001</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>68405.054000000004</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>2299.7007034736707</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4116.7572660765627</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5124.7118226863568</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>6132.9985278331469</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>7127.2488531224744</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>8122.4377062585481</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>9478.70865686867</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>10400.702777364999</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>11332.25882848887</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>12259.93310454397</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>13201.769173888213</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>14605.947038731854</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>15481.536686990439</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>16359.464006457816</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>17255.187742593418</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>18156.716699469773</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>19491.439586367876</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>20405.513898672754</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>21320.105063323543</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>22372.342286031715</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>23151.623948604825</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>24522.915088726986</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>25418.511346607949</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>26312.679330800602</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>27205.506628305815</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>28096.85098426036</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>29614.869429835744</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>30705.607332907421</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>31797.755157938242</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>32898.136117512135</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>34257.800044304015</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>35150.50389985201</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>36041.199287290365</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>37043.598359077492</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>38302.764456082645</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>39148.848018637058</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>39998.386575160432</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>40844.751269442218</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>42207.853020797942</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>43020.726720755163</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>43827.91400483359</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>44639.792832055857</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>46000.083285902525</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>46830.600392743829</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>47663.503810127186</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>48491.311889766628</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>49860.378608965519</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>50960.086368183569</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>52047.412655473105</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>53145.804515541073</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>54508.73496017357</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>55417.27481922185</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>56334.359235444157</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>57246.315791545974</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>58152.846837255282</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>59523.311248863763</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>60429.370507562184</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>61345.635615389867</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>62257.929366330143</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>63156.850910006797</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>64532.570842846457</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>65371.623372722897</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>66204.650382477674</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>66894.900406008324</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>68407.563076223203</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>2366.124696526329</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4192.3963339234369</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5205.1069773136423</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>6216.4712721668539</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>7208.8405468775263</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>8202.5874937414519</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>9558.0519431313314</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>10479.783622635003</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>11411.144371511131</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>12337.65529545603</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>13275.330426111788</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>14674.848161268146</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>15546.846913009562</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>16421.878593542187</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>17308.316057406581</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>18203.249900530227</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>19529.860413632126</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>20438.830701327242</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>21345.443536676459</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>22392.796113968288</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>23168.542251395174</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>24534.257911273016</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>25425.074853392049</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>26318.3554691994</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>27210.000771694187</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>28098.123215739637</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>29615.206370164255</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>30705.83186709258</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>31797.898642061758</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>32898.267682487865</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>34257.964955695985</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>35150.684500147989</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>36041.380512709642</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>37043.758640922511</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>38302.885343917354</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>39148.921981362946</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>39998.401224839574</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>40844.687930557775</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>42207.72177920206</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>43020.551679244832</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>43827.70059516641</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>44639.53696794415</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>45999.793714097468</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46830.292207256178</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>47663.182789872815</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>48490.98311023337</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>49860.052391034478</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>50959.773231816427</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>52047.122544526894</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>53145.558684458934</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>54508.555639826423</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>55417.169380778148</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>56334.34536455584</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>57246.41040845403</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>58153.102562744716</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>59523.711751136238</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>60429.771892437813</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>61345.917384610133</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>62257.973633669862</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>63156.422289993199</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>64531.515957153548</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>65369.967027277104</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>66202.347417522338</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>66891.549393991678</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>68402.544923776804</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F4FC-4FDB-A8A3-348BEC2A64B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="693115136"/>
+        <c:axId val="693118016"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="693115136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693118016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="693118016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693115136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3441,7 +5696,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3998,6 +6809,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>57148</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>323</xdr:row>
+      <xdr:rowOff>133349</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCAA0225-FD84-7E10-8E88-A5140B627D91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7976,7 +10828,7 @@
       </c>
       <c r="D67" s="2">
         <f>D68</f>
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="E67" t="s">
         <v>687</v>
@@ -7995,8 +10847,7 @@
         <v>2332.9126999999999</v>
       </c>
       <c r="D68" s="2">
-        <f>+modelInfo!G4</f>
-        <v>288</v>
+        <v>150</v>
       </c>
       <c r="E68" t="s">
         <v>143</v>
@@ -8015,8 +10866,7 @@
         <v>4154.5767999999998</v>
       </c>
       <c r="D69" s="2">
-        <f>+modelInfo!G5</f>
-        <v>292.79999999999995</v>
+        <v>200</v>
       </c>
       <c r="E69" t="s">
         <v>143</v>
@@ -13205,6 +16055,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13251,9 +16102,8 @@
       <c r="D2" t="s">
         <v>350</v>
       </c>
-      <c r="E2" t="str">
-        <f>modelInfo!J4</f>
-        <v>5C</v>
+      <c r="E2" t="s">
+        <v>691</v>
       </c>
       <c r="F2">
         <v>25</v>
@@ -13274,9 +16124,8 @@
       <c r="D3" t="s">
         <v>350</v>
       </c>
-      <c r="E3" t="str">
-        <f>modelInfo!J5</f>
-        <v>5C</v>
+      <c r="E3" t="s">
+        <v>692</v>
       </c>
       <c r="F3">
         <v>25</v>
